--- a/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:50:27+00:00</t>
+    <t>2026-04-07T13:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T13:39:53+00:00</t>
+    <t>2026-04-08T09:43:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:43:36+00:00</t>
+    <t>2026-04-08T13:03:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5165,7 +5165,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>175</v>
       </c>
@@ -5184,7 +5184,7 @@
         <v>75</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>74</v>
@@ -5569,7 +5569,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
         <v>185</v>
       </c>
@@ -5584,13 +5584,13 @@
         <v>62</v>
       </c>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>74</v>
@@ -5672,7 +5672,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>189</v>
       </c>
@@ -5687,13 +5687,13 @@
         <v>190</v>
       </c>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>74</v>
@@ -5981,7 +5981,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>202</v>
       </c>
@@ -6002,7 +6002,7 @@
         <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>74</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-signes-vitaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
